--- a/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
+++ b/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -527,10 +527,14 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MZL</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -567,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MZL</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -607,7 +615,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -647,7 +659,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
+++ b/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>13.06.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 88 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo - masa resztkowa?. Wskazane badanie MR miednicy -vide opis powyżej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>03.11.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Marginal Zone Lymphoma. Ocena  po 2 cyklach RCVP- przy redukcji rozmiaru nacieku możliwa radioterapia.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 110 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MZL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w topografii przedniej części mięśnia skroniowego po stronie lewej, SUV max 3,7 [Im fuz. 46]. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x10 mm SUV max do 5,8; - okna aortalno-płucnego wielkości do 8 x11 mm SUV max do 4,5; - wnęki płuca lewego średnicy do 10 mm wg PET  SUV max do 4,3; - wnęki płuca prawego średnicy do 11 mm wg PET SUV max do 4,5. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Aktywny metabolicznie rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do S2 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 63x112x 220 mm wg PET SUV max do 10,7.   Aktywne metaboliczne węzły chłonne przy naczyniach biodrowych zewnętrznych lewych średnicy do 12 mm wg PET, SUV max 5,0 [Im fuz. 248].  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 4,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.   Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 4,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej od poziomu Th11 do S2 oraz struktur kostnych kręgosłupa [vide opis powyżej], a także węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>13.02.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Marginal Zone Lymphoma. Ocena  po 6 cyklach RCVP.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 111 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MZL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x15 mm SUV max do 5,4; - okna aortalno-płucnego wielkości do 6 x12 mm SUV max do 3,7; - wnęki płuca lewego średnicy do 11 mm wg PET  SUV max do 4,7; - wnęki płuca prawego średnicy do 17 mm wg PET SUV max do 4,6. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie pobudzony metabolicznie rozległy, nieregularny obszar obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 49x71x154 mm wg PET SUV max do 3,9.   Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.   Wartości referencyjne: MBPS SUVmax 2,6; Prawy płat wątroby SUVmax do 4,0.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono: - pobudzony metabolicznie rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 (częściowa regresja radiologiczna i metaboliczna w porównaniu z badaniem poprzednim). - aktywne metaboliczne węzły chłonne KLP W porównaniu do badania poprzedniego z dnia 03.11.2022 częściowa regresja metaboliczna i radiologiczna ilości i wielkości opisywanych zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>20.06.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>MALT. Ocena  po zakończeniu radio- (13.04.2023) i chemioterapii (12.01.2023).</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 107 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MALT</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny  przytchawiczy dolny prawy wielkości 9 mm, SUV max do 5,4.  Pobudzone metabolicznie węzły chłonne: - wnęki płuca lewego średnicy do 9 mm wg PET,  SUV max do 4,8; - wnęki płuca prawego średnicy do 10 mm wg PET, SUV max do 4,5. Niejednorodnie wzmożony metabolizm FDG w topografii części podstawnej LK po stronie lewobocznej oraz w mniejszym stopniu w przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie, niejednorodnie, pobudzony metabolicznie, rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 -oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym - o orientacyjnych wymiarach: ok. 73x102x119 mm wg PET SUV max do 4,0.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 118x33x84 mm [Im CT 553] - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,0 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.  Wartości referencyjne: MBPS SUVmax 2,4; Prawy płat wątroby SUVmax do 4,9.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - pojedynczego, aktywnego metabolicznie węzła chłonnego przytchawiczego dolnego prawego - jak w badaniu poprzednim  z dnia 13.02.2023. - miernie, niejednorodnie, pobudzonego metabolicznie  nacieku procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej od poziomu Th11 do L5 oraz struktur kostnych kręgosłupa [vide opis powyżej] - jak w badaniu poprzednim z dnia 13.02.2023 Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.4</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>05.09.2024</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>MALT. Ocena  po zakończeniu radio- (13.04.2023) i chemioterapii (12.01.2023). Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 105 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MALT</t>
+          <t>: Miernie pobudzone metabolicznie węzły chłonne grup 4 obustronnie średnicy wg PET do 11mm, SUV max do 3,8. Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie  węzły chłonne:   - przytchawiczy dolny prawy wielkości 13mm, SUV max do 6,7, - okna aortalno płucnego i położone lewobocznie od łuku aorty średnicy do 12mm wg PET, SUV max do 4,4, - podostrogowe średnicy do 9mm wg PET, SUV max do 5,1, - wnęki płuca lewego średnicy do 11mm wg PET,  SUV max do 4,9; - wnęki płuca prawego średnicy do 12mm wg PET, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Wzmożony rysunek podścieliska w segm. 8 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie, niejednorodnie, pobudzony metabolicznie, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej - od poziomu kręgu Th12 do L2 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 o orientacyjnych wymiarach: ok. 30x48x50mm wg PET SUV max do 3,8 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 71x18 mm - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe i najprawdopodobniej fragment pęcherza moczowego, z widoczną w częęści dolnej ok. 39mm przestrzenia płynową -powszerzona pętla jelitowa? inne - wskazana konsultacja chirurgiczna.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 2,6 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.  Wartości referencyjne: MBPS SUVmax 3,2; Prawy płat wątroby SUVmax do 3,7.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnych metabolicznie węzłów chłonnych szyi i śródpiersia; aktualnie ilość widocznych węzłów chłonnych jest nieco większa niż w badaniu PET z dnia 20.06.2024. - miernie, niejednorodnie, pobudzonego metabolicznie  nacieku procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej - w porównaniu do badania poprzednim z dnia 20.06.2024 częściowa regresja wielkości i aktywności metabolicznej zmiany. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>6.7</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
+++ b/pacjenci/EUGENIUSZ RACHWAŁ.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 88 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo - masa resztkowa?. Wskazane badanie MR miednicy -vide opis powyżej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 110 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w topografii przedniej części mięśnia skroniowego po stronie lewej, SUV max 3,7 [Im fuz. 46]. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x10 mm SUV max do 5,8; - okna aortalno-płucnego wielkości do 8 x11 mm SUV max do 4,5; - wnęki płuca lewego średnicy do 10 mm wg PET  SUV max do 4,3; - wnęki płuca prawego średnicy do 11 mm wg PET SUV max do 4,5. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Aktywny metabolicznie rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do S2 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 63x112x 220 mm wg PET SUV max do 10,7.   Aktywne metaboliczne węzły chłonne przy naczyniach biodrowych zewnętrznych lewych średnicy do 12 mm wg PET, SUV max 5,0 [Im fuz. 248].  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 4,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.   Wartości referencyjne: MBPS SUVmax 2,7; Prawy płat wątroby SUVmax do 4,2.</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w topografii przedniej części mięśnia skroniowego po stronie lewej, SUV max 3,7 [Im fuz. 46]. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x10 mm SUV max do 5,8; - okna aortalno-płucnego wielkości do 8 x11 mm SUV max do 4,5; - wnęki płuca lewego średnicy do 10 mm wg PET  SUV max do 4,3; - wnęki płuca prawego średnicy do 11 mm wg PET SUV max do 4,5. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do S2 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 63x112x 220 mm wg PET SUV max do 10,7.   Aktywne metaboliczne węzły chłonne przy naczyniach biodrowych zewnętrznych lewych średnicy do 12 mm wg PET, SUV max 5,0 [Im fuz. 248].  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 4,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej od poziomu Th11 do S2 oraz struktur kostnych kręgosłupa [vide opis powyżej], a także węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 111 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x15 mm SUV max do 5,4; - okna aortalno-płucnego wielkości do 6 x12 mm SUV max do 3,7; - wnęki płuca lewego średnicy do 11 mm wg PET  SUV max do 4,7; - wnęki płuca prawego średnicy do 17 mm wg PET SUV max do 4,6. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie pobudzony metabolicznie rozległy, nieregularny obszar obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 49x71x154 mm wg PET SUV max do 3,9.   Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.   Wartości referencyjne: MBPS SUVmax 2,6; Prawy płat wątroby SUVmax do 4,0.</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aktywne metaboliczne węzły chłonne: - przytchawicze dolne prawe wielkości do 8x15 mm SUV max do 5,4; - okna aortalno-płucnego wielkości do 6 x12 mm SUV max do 3,7; - wnęki płuca lewego średnicy do 11 mm wg PET  SUV max do 4,7; - wnęki płuca prawego średnicy do 17 mm wg PET SUV max do 4,6. Niejednorodny metabolizm FDG w topografii części podstawnej LK oraz przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Miernie pobudzony metabolicznie rozległy, nieregularny obszar obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK] o łącznej wielkości ok. 49x71x154 mm wg PET SUV max do 3,9.   Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca pętle jelitowe.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,2 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono: - pobudzony metabolicznie rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 (częściowa regresja radiologiczna i metaboliczna w porównaniu z badaniem poprzednim). - aktywne metaboliczne węzły chłonne KLP W porównaniu do badania poprzedniego z dnia 03.11.2022 częściowa regresja metaboliczna i radiologiczna ilości i wielkości opisywanych zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 107 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny  przytchawiczy dolny prawy wielkości 9 mm, SUV max do 5,4.  Pobudzone metabolicznie węzły chłonne: - wnęki płuca lewego średnicy do 9 mm wg PET,  SUV max do 4,8; - wnęki płuca prawego średnicy do 10 mm wg PET, SUV max do 4,5. Niejednorodnie wzmożony metabolizm FDG w topografii części podstawnej LK po stronie lewobocznej oraz w mniejszym stopniu w przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie, niejednorodnie, pobudzony metabolicznie, rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 -oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym - o orientacyjnych wymiarach: ok. 73x102x119 mm wg PET SUV max do 4,0.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 118x33x84 mm [Im CT 553] - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,0 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.  Wartości referencyjne: MBPS SUVmax 2,4; Prawy płat wątroby SUVmax do 4,9.</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny  przytchawiczy dolny prawy wielkości 9 mm, SUV max do 5,4.  Pobudzone metabolicznie węzły chłonne: - wnęki płuca lewego średnicy do 9 mm wg PET,  SUV max do 4,8; - wnęki płuca prawego średnicy do 10 mm wg PET, SUV max do 4,5. Niejednorodnie wzmożony metabolizm FDG w topografii części podstawnej LK po stronie lewobocznej oraz w mniejszym stopniu w przypodstawnej części przegrody międzykomorowej - do ew. oceny w Echokardiografii/badaniu Cardio-MR.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Miernie, niejednorodnie, pobudzony metabolicznie, rozległy, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej i w części grzbietowej - od poziomu kręgu Th11 do L5 -oraz struktury kostne, głównie wyrostki poprzeczne prawe kręgów L1-L4 oraz małe stawy międzykręgowe po stronie prawej, zwłaszcza na poziomie Th12/L1, L1/L2, L2/L3 i L3/L4 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym - o orientacyjnych wymiarach: ok. 73x102x119 mm wg PET SUV max do 4,0.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 118x33x84 mm [Im CT 553] - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 5,0 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - pojedynczego, aktywnego metabolicznie węzła chłonnego przytchawiczego dolnego prawego - jak w badaniu poprzednim  z dnia 13.02.2023. - miernie, niejednorodnie, pobudzonego metabolicznie  nacieku procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej od poziomu Th11 do L5 oraz struktur kostnych kręgosłupa [vide opis powyżej] - jak w badaniu poprzednim z dnia 13.02.2023 Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 105 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie węzły chłonne grup 4 obustronnie średnicy wg PET do 11mm, SUV max do 3,8. Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie  węzły chłonne:   - przytchawiczy dolny prawy wielkości 13mm, SUV max do 6,7, - okna aortalno płucnego i położone lewobocznie od łuku aorty średnicy do 12mm wg PET, SUV max do 4,4, - podostrogowe średnicy do 9mm wg PET, SUV max do 5,1, - wnęki płuca lewego średnicy do 11mm wg PET,  SUV max do 4,9; - wnęki płuca prawego średnicy do 12mm wg PET, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Wzmożony rysunek podścieliska w segm. 8 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie, niejednorodnie, pobudzony metabolicznie, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej - od poziomu kręgu Th12 do L2 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 o orientacyjnych wymiarach: ok. 30x48x50mm wg PET SUV max do 3,8 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 71x18 mm - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe i najprawdopodobniej fragment pęcherza moczowego, z widoczną w częęści dolnej ok. 39mm przestrzenia płynową -powszerzona pętla jelitowa? inne - wskazana konsultacja chirurgiczna.  Układ kostny: Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 2,6 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.  Wartości referencyjne: MBPS SUVmax 3,2; Prawy płat wątroby SUVmax do 3,7.</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne grup 4 obustronnie średnicy wg PET do 11mm, SUV max do 3,8. Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Komory boczne mózgu miernie poszerzone - niewielki podkorowy zanik mózgu. Niewielkie prawowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie  węzły chłonne:   - przytchawiczy dolny prawy wielkości 13mm, SUV max do 6,7, - okna aortalno płucnego i położone lewobocznie od łuku aorty średnicy do 12mm wg PET, SUV max do 4,4, - podostrogowe średnicy do 9mm wg PET, SUV max do 5,1, - wnęki płuca lewego średnicy do 11mm wg PET,  SUV max do 4,9; - wnęki płuca prawego średnicy do 12mm wg PET, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz w segmencie 3 płuca lewego. Uwapniony guzek w segmencie 4/5 płuca lewego średnicy 6 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Wzmożony rysunek podścieliska w segm. 8 płuca lewego. Drobne pęcherze rozedmowe w płatach dolnych obu płuc, niektóre, zwłaszcza w segm. 10 płuca lewego z zagęszczeniami miąższowymi wokół. Węzeł chłonny przykręgosłupowy na poziomie Th11/Th12 po stronie prawej średnicy 9 mm. Niewielkie pasmowate zmiany włókniste w segm. 4 i nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Miernie, niejednorodnie, pobudzony metabolicznie, nieregularny naciek obejmujący mięśnie przykręgosłupowe po stronie prawej - od poziomu kręgu Th12 do L2 - z częściową ich destrukcją [stan po odbarczeniu kanału kręgowego na poziomie L1-L2, z usunięciem wyrostków kolczystych na tych poziomach oraz najprawdopodobniej części wyrostka na poziomie Th12 o orientacyjnych wymiarach: ok. 30x48x50mm wg PET SUV max do 3,8 - dokładna ocena możliwa w badaniu celowanym TK/MR z kontrastem dożylnym.  Niejednorodny metabolizm FDG w wątrobie. Niejednorodny metabolizm FDG w gruczole krokowym, ze zwapnieniami - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywna metabolicznie masa miękkotkankowa w tkance podskórnej okolicy krzyżowej wielkości ok 71x18 mm - dokładna ocena możliwa j.w. Mierne pogrubienie trzonu nadnercza lewego. Nerka lewa o nieco pozaciąganych pozapalnie obrysach. Przepuklina pachwinowa po stronie prawej - zawierająca w części górnej pętle jelitowe i najprawdopodobniej fragment pęcherza moczowego, z widoczną w częęści dolnej ok. 39mm przestrzenia płynową -powszerzona pętla jelitowa? inne - wskazana konsultacja chirurgiczna.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG wokół stawu ramiennego lewego, z nasilonymi zmianami zwyrodnieniowymi, SUV max do 2,6 - w pierwszej kolejności zmiany przeciążeniowo-zwyrodnieniowo-odczynowe. Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kregosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego oraz nieznaczna lewowypukła kręgosłupa lędźwiowego, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych - wydatne po stronie lewej, z mostem kostnym. Os sacrum arcuatum. Zmiany zwyrodnieniowe w stawach biodrowych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnych metabolicznie węzłów chłonnych szyi i śródpiersia; aktualnie ilość widocznych węzłów chłonnych jest nieco większa niż w badaniu PET z dnia 20.06.2024. - miernie, niejednorodnie, pobudzonego metabolicznie  nacieku procesu chłoniakowego z zajęciem mięśni przykręgosłupowych po stronie prawej - w porównaniu do badania poprzednim z dnia 20.06.2024 częściowa regresja wielkości i aktywności metabolicznej zmiany. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>6.7</v>
       </c>
     </row>
